--- a/data/nzd0425/nzd0425.xlsx
+++ b/data/nzd0425/nzd0425.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC318"/>
+  <dimension ref="A1:AC320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29641,7 +29641,7 @@
         <v>420.89</v>
       </c>
       <c r="R316" t="n">
-        <v>389.97</v>
+        <v>380.57</v>
       </c>
       <c r="S316" t="n">
         <v>321.91</v>
@@ -29734,10 +29734,10 @@
         <v>436.43</v>
       </c>
       <c r="R317" t="n">
-        <v>384.14</v>
+        <v>359.34</v>
       </c>
       <c r="S317" t="n">
-        <v>304.55</v>
+        <v>293.96</v>
       </c>
       <c r="T317" t="n">
         <v>376.68</v>
@@ -29827,10 +29827,10 @@
         <v>444.89</v>
       </c>
       <c r="R318" t="n">
-        <v>397.82</v>
+        <v>352.66</v>
       </c>
       <c r="S318" t="n">
-        <v>300.49</v>
+        <v>285.02</v>
       </c>
       <c r="T318" t="n">
         <v>415.81</v>
@@ -29839,7 +29839,7 @@
         <v>392.31</v>
       </c>
       <c r="V318" t="n">
-        <v>367.25</v>
+        <v>377.43</v>
       </c>
       <c r="W318" t="n">
         <v>351.11</v>
@@ -29862,6 +29862,192 @@
       <c r="AC318" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:19:27+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>366.86</v>
+      </c>
+      <c r="C319" t="n">
+        <v>358.3</v>
+      </c>
+      <c r="D319" t="n">
+        <v>361.77</v>
+      </c>
+      <c r="E319" t="n">
+        <v>367.87</v>
+      </c>
+      <c r="F319" t="n">
+        <v>368.21</v>
+      </c>
+      <c r="G319" t="n">
+        <v>372.18</v>
+      </c>
+      <c r="H319" t="n">
+        <v>383.13</v>
+      </c>
+      <c r="I319" t="n">
+        <v>397.24</v>
+      </c>
+      <c r="J319" t="n">
+        <v>419.6</v>
+      </c>
+      <c r="K319" t="n">
+        <v>419.12</v>
+      </c>
+      <c r="L319" t="n">
+        <v>421.41</v>
+      </c>
+      <c r="M319" t="n">
+        <v>428.67</v>
+      </c>
+      <c r="N319" t="n">
+        <v>442.81</v>
+      </c>
+      <c r="O319" t="n">
+        <v>452.88</v>
+      </c>
+      <c r="P319" t="n">
+        <v>453.96</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>452.95</v>
+      </c>
+      <c r="R319" t="n">
+        <v>249.09</v>
+      </c>
+      <c r="S319" t="n">
+        <v>214.19</v>
+      </c>
+      <c r="T319" t="n">
+        <v>454.95</v>
+      </c>
+      <c r="U319" t="n">
+        <v>434</v>
+      </c>
+      <c r="V319" t="n">
+        <v>497.12</v>
+      </c>
+      <c r="W319" t="n">
+        <v>342.43</v>
+      </c>
+      <c r="X319" t="n">
+        <v>351.24</v>
+      </c>
+      <c r="Y319" t="n">
+        <v>338.94</v>
+      </c>
+      <c r="Z319" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="AA319" t="n">
+        <v>317.35</v>
+      </c>
+      <c r="AB319" t="n">
+        <v>309.62</v>
+      </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:19:44+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>368.79</v>
+      </c>
+      <c r="C320" t="n">
+        <v>358.82</v>
+      </c>
+      <c r="D320" t="n">
+        <v>361.97</v>
+      </c>
+      <c r="E320" t="n">
+        <v>370.66</v>
+      </c>
+      <c r="F320" t="n">
+        <v>369.7</v>
+      </c>
+      <c r="G320" t="n">
+        <v>374</v>
+      </c>
+      <c r="H320" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="I320" t="n">
+        <v>397.08</v>
+      </c>
+      <c r="J320" t="n">
+        <v>417.57</v>
+      </c>
+      <c r="K320" t="n">
+        <v>416.45</v>
+      </c>
+      <c r="L320" t="n">
+        <v>421.41</v>
+      </c>
+      <c r="M320" t="n">
+        <v>428.67</v>
+      </c>
+      <c r="N320" t="n">
+        <v>442.81</v>
+      </c>
+      <c r="O320" t="n">
+        <v>452.88</v>
+      </c>
+      <c r="P320" t="n">
+        <v>453.96</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>452.95</v>
+      </c>
+      <c r="R320" t="n">
+        <v>249.09</v>
+      </c>
+      <c r="S320" t="n">
+        <v>214.19</v>
+      </c>
+      <c r="T320" t="n">
+        <v>454.95</v>
+      </c>
+      <c r="U320" t="n">
+        <v>434</v>
+      </c>
+      <c r="V320" t="n">
+        <v>497.12</v>
+      </c>
+      <c r="W320" t="n">
+        <v>342.43</v>
+      </c>
+      <c r="X320" t="n">
+        <v>351.24</v>
+      </c>
+      <c r="Y320" t="n">
+        <v>338.94</v>
+      </c>
+      <c r="Z320" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="AA320" t="n">
+        <v>317.35</v>
+      </c>
+      <c r="AB320" t="n">
+        <v>309.62</v>
+      </c>
+      <c r="AC320" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -29876,7 +30062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B322"/>
+  <dimension ref="A1:B324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33099,6 +33285,26 @@
       </c>
       <c r="B322" t="n">
         <v>1.06</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>
@@ -33267,28 +33473,28 @@
         <v>0.1361</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.765058286118645</v>
+        <v>-0.7651263176104314</v>
       </c>
       <c r="J2" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K2" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2112383647177463</v>
+        <v>0.2136528005275372</v>
       </c>
       <c r="M2" t="n">
-        <v>8.474550436100548</v>
+        <v>8.427501731092294</v>
       </c>
       <c r="N2" t="n">
-        <v>121.3115780047257</v>
+        <v>120.5569535436073</v>
       </c>
       <c r="O2" t="n">
-        <v>11.01415353101298</v>
+        <v>10.97984305641967</v>
       </c>
       <c r="P2" t="n">
-        <v>388.2783555225473</v>
+        <v>388.2790610855527</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33345,28 +33551,28 @@
         <v>0.1113</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8022313221034841</v>
+        <v>-0.8097232088775621</v>
       </c>
       <c r="J3" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K3" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1450633614858644</v>
+        <v>0.1490581610789882</v>
       </c>
       <c r="M3" t="n">
-        <v>10.97088152794117</v>
+        <v>10.93849553050753</v>
       </c>
       <c r="N3" t="n">
-        <v>210.5308019879755</v>
+        <v>209.4293394706811</v>
       </c>
       <c r="O3" t="n">
-        <v>14.50967959632381</v>
+        <v>14.47167369279314</v>
       </c>
       <c r="P3" t="n">
-        <v>385.9112707035142</v>
+        <v>385.9896236862169</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33423,28 +33629,28 @@
         <v>0.1963</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6568109341641151</v>
+        <v>-0.6677475244621592</v>
       </c>
       <c r="J4" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K4" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09585868116500296</v>
+        <v>0.09985392553283967</v>
       </c>
       <c r="M4" t="n">
-        <v>11.3064863976705</v>
+        <v>11.30850716512076</v>
       </c>
       <c r="N4" t="n">
-        <v>225.8529870701297</v>
+        <v>224.9016552602567</v>
       </c>
       <c r="O4" t="n">
-        <v>15.02840600563246</v>
+        <v>14.99672148371959</v>
       </c>
       <c r="P4" t="n">
-        <v>388.0843917200789</v>
+        <v>388.198772426297</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33501,28 +33707,28 @@
         <v>0.1229</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5710181888962134</v>
+        <v>-0.5882837233664682</v>
       </c>
       <c r="J5" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K5" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0535686823171847</v>
+        <v>0.05724147833193227</v>
       </c>
       <c r="M5" t="n">
-        <v>14.2493416178674</v>
+        <v>14.26562341678412</v>
       </c>
       <c r="N5" t="n">
-        <v>319.7556647761453</v>
+        <v>318.9212956676512</v>
       </c>
       <c r="O5" t="n">
-        <v>17.88171313873884</v>
+        <v>17.85836766526133</v>
       </c>
       <c r="P5" t="n">
-        <v>398.2231877616252</v>
+        <v>398.4037524496577</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33579,28 +33785,28 @@
         <v>0.1248</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4982729894014674</v>
+        <v>-0.5104249995279964</v>
       </c>
       <c r="J6" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K6" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03688359621498449</v>
+        <v>0.03910792907586114</v>
       </c>
       <c r="M6" t="n">
-        <v>14.95693271989779</v>
+        <v>14.93991409452051</v>
       </c>
       <c r="N6" t="n">
-        <v>359.4859066144924</v>
+        <v>357.8019815610132</v>
       </c>
       <c r="O6" t="n">
-        <v>18.96011357071714</v>
+        <v>18.91565440477842</v>
       </c>
       <c r="P6" t="n">
-        <v>391.8898914712651</v>
+        <v>392.0172254351936</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33657,28 +33863,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4164928392943164</v>
+        <v>-0.4192737202226078</v>
       </c>
       <c r="J7" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K7" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02686462051711802</v>
+        <v>0.0275932440977239</v>
       </c>
       <c r="M7" t="n">
-        <v>14.76271970541921</v>
+        <v>14.6873910019256</v>
       </c>
       <c r="N7" t="n">
-        <v>348.7770127169951</v>
+        <v>346.625666889415</v>
       </c>
       <c r="O7" t="n">
-        <v>18.67557262085945</v>
+        <v>18.61788567183221</v>
       </c>
       <c r="P7" t="n">
-        <v>386.4096178242402</v>
+        <v>386.4386963175983</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33735,28 +33941,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1307010987081659</v>
+        <v>-0.1250691165796506</v>
       </c>
       <c r="J8" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K8" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002355202695276115</v>
+        <v>0.002187344900420829</v>
       </c>
       <c r="M8" t="n">
-        <v>15.60803607692525</v>
+        <v>15.52835763176416</v>
       </c>
       <c r="N8" t="n">
-        <v>401.6486881229928</v>
+        <v>399.2566272978462</v>
       </c>
       <c r="O8" t="n">
-        <v>20.04117481893197</v>
+        <v>19.98140703999211</v>
       </c>
       <c r="P8" t="n">
-        <v>382.8211959440072</v>
+        <v>382.7622891272622</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33813,28 +34019,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08714010404689129</v>
+        <v>0.1028641139818463</v>
       </c>
       <c r="J9" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K9" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009709769223656961</v>
+        <v>0.001368901311614268</v>
       </c>
       <c r="M9" t="n">
-        <v>15.76626032017078</v>
+        <v>15.72070985806545</v>
       </c>
       <c r="N9" t="n">
-        <v>433.6562092764889</v>
+        <v>431.8977640103425</v>
       </c>
       <c r="O9" t="n">
-        <v>20.8244137799</v>
+        <v>20.78215012962669</v>
       </c>
       <c r="P9" t="n">
-        <v>382.3324141544667</v>
+        <v>382.1679635700237</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33891,28 +34097,28 @@
         <v>0.1309</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3830118937716538</v>
+        <v>0.4141919256858329</v>
       </c>
       <c r="J10" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K10" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01771176643247618</v>
+        <v>0.02077072658120116</v>
       </c>
       <c r="M10" t="n">
-        <v>16.54573337391897</v>
+        <v>16.57730392277556</v>
       </c>
       <c r="N10" t="n">
-        <v>451.5873937063334</v>
+        <v>452.5391799203917</v>
       </c>
       <c r="O10" t="n">
-        <v>21.25058572619431</v>
+        <v>21.2729682912468</v>
       </c>
       <c r="P10" t="n">
-        <v>383.5772567819682</v>
+        <v>383.2511636827699</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33969,28 +34175,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6788654373658167</v>
+        <v>0.7071725007039111</v>
       </c>
       <c r="J11" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K11" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05483960691724865</v>
+        <v>0.05963410091352539</v>
       </c>
       <c r="M11" t="n">
-        <v>16.69137755312211</v>
+        <v>16.70357411590384</v>
       </c>
       <c r="N11" t="n">
-        <v>440.8783790377346</v>
+        <v>441.2382503839069</v>
       </c>
       <c r="O11" t="n">
-        <v>20.99710406312581</v>
+        <v>21.00567186223537</v>
       </c>
       <c r="P11" t="n">
-        <v>377.1701636638404</v>
+        <v>376.8741197315835</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34047,28 +34253,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8867526427697029</v>
+        <v>0.9184473932663361</v>
       </c>
       <c r="J12" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K12" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L12" t="n">
-        <v>0.07909819782162741</v>
+        <v>0.08487964278473792</v>
       </c>
       <c r="M12" t="n">
-        <v>18.07701888233137</v>
+        <v>18.09334582319161</v>
       </c>
       <c r="N12" t="n">
-        <v>508.1500127361812</v>
+        <v>508.866047191839</v>
       </c>
       <c r="O12" t="n">
-        <v>22.54218296297369</v>
+        <v>22.55805947309828</v>
       </c>
       <c r="P12" t="n">
-        <v>372.560492956756</v>
+        <v>372.2290104406195</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34125,28 +34331,28 @@
         <v>0.1835</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7749334144149482</v>
+        <v>0.8114347424838836</v>
       </c>
       <c r="J13" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K13" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05650639027325421</v>
+        <v>0.0619083011444268</v>
       </c>
       <c r="M13" t="n">
-        <v>18.71975903722932</v>
+        <v>18.75531391113129</v>
       </c>
       <c r="N13" t="n">
-        <v>556.557958479106</v>
+        <v>558.2437032308336</v>
       </c>
       <c r="O13" t="n">
-        <v>23.59148063346398</v>
+        <v>23.62718144914525</v>
       </c>
       <c r="P13" t="n">
-        <v>378.9774078961873</v>
+        <v>378.5956553218941</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34203,28 +34409,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7563974826818306</v>
+        <v>0.8075920513202618</v>
       </c>
       <c r="J14" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K14" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05819412620794417</v>
+        <v>0.06546895714306777</v>
       </c>
       <c r="M14" t="n">
-        <v>18.66979630011054</v>
+        <v>18.75193958354734</v>
       </c>
       <c r="N14" t="n">
-        <v>513.9520662230209</v>
+        <v>520.9098985481032</v>
       </c>
       <c r="O14" t="n">
-        <v>22.67051093872877</v>
+        <v>22.82345062754761</v>
       </c>
       <c r="P14" t="n">
-        <v>381.9293953651173</v>
+        <v>381.3939721295873</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34281,28 +34487,28 @@
         <v>0.0862</v>
       </c>
       <c r="I15" t="n">
-        <v>0.296502198160094</v>
+        <v>0.3666464168273637</v>
       </c>
       <c r="J15" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K15" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L15" t="n">
-        <v>0.006142697673878872</v>
+        <v>0.009278270759502272</v>
       </c>
       <c r="M15" t="n">
-        <v>23.12602713022644</v>
+        <v>23.2037513874241</v>
       </c>
       <c r="N15" t="n">
-        <v>791.6792418543463</v>
+        <v>805.5074124393016</v>
       </c>
       <c r="O15" t="n">
-        <v>28.13679515961877</v>
+        <v>28.3814624788664</v>
       </c>
       <c r="P15" t="n">
-        <v>389.8450992479596</v>
+        <v>389.1148085189028</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34359,28 +34565,28 @@
         <v>0.08890000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2782649040226067</v>
+        <v>0.3625828432279433</v>
       </c>
       <c r="J16" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K16" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L16" t="n">
-        <v>0.002015896413553819</v>
+        <v>0.003423492549534224</v>
       </c>
       <c r="M16" t="n">
-        <v>31.50528954159487</v>
+        <v>31.47061420848349</v>
       </c>
       <c r="N16" t="n">
-        <v>2070.600467726993</v>
+        <v>2084.051021234047</v>
       </c>
       <c r="O16" t="n">
-        <v>45.50385113072291</v>
+        <v>45.65140765884495</v>
       </c>
       <c r="P16" t="n">
-        <v>381.086765521202</v>
+        <v>380.1871357271554</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34437,28 +34643,28 @@
         <v>0.0687</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5721792291548021</v>
+        <v>0.679189088730121</v>
       </c>
       <c r="J17" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K17" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L17" t="n">
-        <v>0.009501194537716806</v>
+        <v>0.01324983219463982</v>
       </c>
       <c r="M17" t="n">
-        <v>30.88352087226086</v>
+        <v>31.03601404889949</v>
       </c>
       <c r="N17" t="n">
-        <v>1828.060386249223</v>
+        <v>1856.260053725682</v>
       </c>
       <c r="O17" t="n">
-        <v>42.75582283443067</v>
+        <v>43.08433652414392</v>
       </c>
       <c r="P17" t="n">
-        <v>358.3654694764211</v>
+        <v>357.2259460232734</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -34519,28 +34725,28 @@
         <v>0.0464</v>
       </c>
       <c r="I18" t="n">
-        <v>2.385801890885276</v>
+        <v>2.149128678937242</v>
       </c>
       <c r="J18" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K18" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2536311777051158</v>
+        <v>0.1954074155487774</v>
       </c>
       <c r="M18" t="n">
-        <v>23.3502966636797</v>
+        <v>24.43074842839059</v>
       </c>
       <c r="N18" t="n">
-        <v>949.4406902204105</v>
+        <v>1086.438986380565</v>
       </c>
       <c r="O18" t="n">
-        <v>30.81299547626635</v>
+        <v>32.96117392297436</v>
       </c>
       <c r="P18" t="n">
-        <v>329.5976518148578</v>
+        <v>332.0609341320369</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -34601,28 +34807,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9320751026111869</v>
+        <v>0.7127597845348451</v>
       </c>
       <c r="J19" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K19" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L19" t="n">
-        <v>0.02615511074465571</v>
+        <v>0.0143515687782626</v>
       </c>
       <c r="M19" t="n">
-        <v>30.84151219664748</v>
+        <v>32.05776224759364</v>
       </c>
       <c r="N19" t="n">
-        <v>1818.383858901125</v>
+        <v>1977.361850608272</v>
       </c>
       <c r="O19" t="n">
-        <v>42.6425123427446</v>
+        <v>44.46753704229943</v>
       </c>
       <c r="P19" t="n">
-        <v>347.2016727980914</v>
+        <v>349.4788473585328</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -34683,28 +34889,28 @@
         <v>0.0269</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1531605450766317</v>
+        <v>-0.02627706215553786</v>
       </c>
       <c r="J20" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K20" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0009675333086874849</v>
+        <v>2.768007134579253e-05</v>
       </c>
       <c r="M20" t="n">
-        <v>24.68791213143895</v>
+        <v>25.06395795586282</v>
       </c>
       <c r="N20" t="n">
-        <v>1394.942966401956</v>
+        <v>1448.079086247053</v>
       </c>
       <c r="O20" t="n">
-        <v>37.34893527802307</v>
+        <v>38.05363433690733</v>
       </c>
       <c r="P20" t="n">
-        <v>362.0428641401106</v>
+        <v>360.7355955358569</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -34765,28 +34971,28 @@
         <v>0.0312</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8929883712610305</v>
+        <v>-0.76667689402568</v>
       </c>
       <c r="J21" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K21" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02371195058944686</v>
+        <v>0.01726356942736529</v>
       </c>
       <c r="M21" t="n">
-        <v>30.14009652528887</v>
+        <v>30.44721498517852</v>
       </c>
       <c r="N21" t="n">
-        <v>1848.683013905758</v>
+        <v>1899.045296745189</v>
       </c>
       <c r="O21" t="n">
-        <v>42.99631395719589</v>
+        <v>43.57803686199263</v>
       </c>
       <c r="P21" t="n">
-        <v>358.6505247957959</v>
+        <v>357.3348643345932</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -34847,28 +35053,28 @@
         <v>0.0247</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6933845951595676</v>
+        <v>0.8605949570779163</v>
       </c>
       <c r="J22" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K22" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="L22" t="n">
-        <v>0.03972096026987948</v>
+        <v>0.05308590074417752</v>
       </c>
       <c r="M22" t="n">
-        <v>19.17696235582643</v>
+        <v>19.77939653984897</v>
       </c>
       <c r="N22" t="n">
-        <v>648.4595453761974</v>
+        <v>743.0802133931752</v>
       </c>
       <c r="O22" t="n">
-        <v>25.46486884663256</v>
+        <v>27.25949767316293</v>
       </c>
       <c r="P22" t="n">
-        <v>353.1115352211373</v>
+        <v>351.3697513734327</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -34929,28 +35135,28 @@
         <v>0.0528</v>
       </c>
       <c r="I23" t="n">
-        <v>1.197652455554666</v>
+        <v>1.164461740646493</v>
       </c>
       <c r="J23" t="n">
+        <v>319</v>
+      </c>
+      <c r="K23" t="n">
         <v>317</v>
       </c>
-      <c r="K23" t="n">
-        <v>315</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.1698626653077376</v>
+        <v>0.1625267818232569</v>
       </c>
       <c r="M23" t="n">
-        <v>15.09407007691573</v>
+        <v>15.19996657426504</v>
       </c>
       <c r="N23" t="n">
-        <v>390.2576110879125</v>
+        <v>392.0926424989547</v>
       </c>
       <c r="O23" t="n">
-        <v>19.75493890367451</v>
+        <v>19.80132931141126</v>
       </c>
       <c r="P23" t="n">
-        <v>336.8635487581577</v>
+        <v>337.2106769588792</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -35007,28 +35213,28 @@
         <v>0.0794</v>
       </c>
       <c r="I24" t="n">
-        <v>1.148164941859609</v>
+        <v>1.129102736857184</v>
       </c>
       <c r="J24" t="n">
+        <v>319</v>
+      </c>
+      <c r="K24" t="n">
         <v>317</v>
       </c>
-      <c r="K24" t="n">
-        <v>315</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.1374449038356337</v>
+        <v>0.1348233971624708</v>
       </c>
       <c r="M24" t="n">
-        <v>16.69784290571835</v>
+        <v>16.67490126879613</v>
       </c>
       <c r="N24" t="n">
-        <v>458.30263861419</v>
+        <v>456.8215456826809</v>
       </c>
       <c r="O24" t="n">
-        <v>21.40800407824583</v>
+        <v>21.37338404845337</v>
       </c>
       <c r="P24" t="n">
-        <v>335.7287247067745</v>
+        <v>335.9288525370008</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -35085,28 +35291,28 @@
         <v>0.1141</v>
       </c>
       <c r="I25" t="n">
-        <v>1.10383634000211</v>
+        <v>1.090777972399203</v>
       </c>
       <c r="J25" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K25" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1366608424529365</v>
+        <v>0.1353589062444259</v>
       </c>
       <c r="M25" t="n">
-        <v>15.94639889455561</v>
+        <v>15.90167731042217</v>
       </c>
       <c r="N25" t="n">
-        <v>428.1092526460134</v>
+        <v>426.0813031869384</v>
       </c>
       <c r="O25" t="n">
-        <v>20.6908011600811</v>
+        <v>20.64173692272379</v>
       </c>
       <c r="P25" t="n">
-        <v>319.89010144233</v>
+        <v>320.0266503951221</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -35163,28 +35369,28 @@
         <v>0.2</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9402855808199593</v>
+        <v>0.9397476851348782</v>
       </c>
       <c r="J26" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K26" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1177001874025041</v>
+        <v>0.1190731594870237</v>
       </c>
       <c r="M26" t="n">
-        <v>15.14930472199548</v>
+        <v>15.05714690010798</v>
       </c>
       <c r="N26" t="n">
-        <v>367.8737580040364</v>
+        <v>365.5684638989624</v>
       </c>
       <c r="O26" t="n">
-        <v>19.18003540153241</v>
+        <v>19.11984476660212</v>
       </c>
       <c r="P26" t="n">
-        <v>300.8534695106718</v>
+        <v>300.8590952070771</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -35241,28 +35447,28 @@
         <v>0.2</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8779783972485798</v>
+        <v>0.8856811523424412</v>
       </c>
       <c r="J27" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K27" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1212264258197652</v>
+        <v>0.1245705607128158</v>
       </c>
       <c r="M27" t="n">
-        <v>13.91436776710507</v>
+        <v>13.86271311918492</v>
       </c>
       <c r="N27" t="n">
-        <v>310.1612739450636</v>
+        <v>308.4471508739169</v>
       </c>
       <c r="O27" t="n">
-        <v>17.61139613844012</v>
+        <v>17.56266354725037</v>
       </c>
       <c r="P27" t="n">
-        <v>287.8091149155528</v>
+        <v>287.7285549744644</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -35319,28 +35525,28 @@
         <v>0.121</v>
       </c>
       <c r="I28" t="n">
-        <v>0.900700118446592</v>
+        <v>0.9099626939368448</v>
       </c>
       <c r="J28" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K28" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1465702771276635</v>
+        <v>0.1508087971056146</v>
       </c>
       <c r="M28" t="n">
-        <v>12.92688398266928</v>
+        <v>12.89281836942874</v>
       </c>
       <c r="N28" t="n">
-        <v>262.1938607717376</v>
+        <v>260.8832617186483</v>
       </c>
       <c r="O28" t="n">
-        <v>16.19240132814579</v>
+        <v>16.15188105821264</v>
       </c>
       <c r="P28" t="n">
-        <v>278.232754440476</v>
+        <v>278.1358809703003</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -35378,7 +35584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC318"/>
+  <dimension ref="A1:AC320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81386,7 +81592,7 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>-43.21944464511276,170.16091190988672</t>
+          <t>-43.21951180504154,170.1609822303193</t>
         </is>
       </c>
       <c r="S316" t="inlineStr">
@@ -81533,12 +81739,12 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>-43.219486298562614,170.1609555234987</t>
+          <t>-43.21966348630934,170.16114105032716</t>
         </is>
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>-43.219670234013726,170.1622567568168</t>
+          <t>-43.21974778677371,170.162332484663</t>
         </is>
       </c>
       <c r="T317" t="inlineStr">
@@ -81680,12 +81886,12 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>-43.219388559397196,170.16085318496184</t>
+          <t>-43.21971121263913,170.16119102305817</t>
         </is>
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>-43.219699966238714,170.16228578937753</t>
+          <t>-43.21981325620689,170.1623964137007</t>
         </is>
       </c>
       <c r="T318" t="inlineStr">
@@ -81700,7 +81906,7 @@
       </c>
       <c r="V318" t="inlineStr">
         <is>
-          <t>-43.21803442774098,170.1639661030855</t>
+          <t>-43.2179598780657,170.1638933078492</t>
         </is>
       </c>
       <c r="W318" t="inlineStr">
@@ -81736,6 +81942,300 @@
       <c r="AC318" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-18 22:19:27+00:00</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>-43.2260894887096,170.15017442177611</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>-43.22593417509935,170.1510508935484</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>-43.225676565941725,170.1518789191563</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>-43.22540693650193,170.15265989822765</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-43.22503130981617,170.15333406837007</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>-43.22459278067127,170.1539968877721</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>-43.224102251173065,170.15461159350693</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>-43.223589251736385,170.15520246408803</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>-43.2230396515101,170.15569360764675</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>-43.22261250104492,170.15628078179597</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>-43.22212531571023,170.15685479160302</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>-43.22159770273849,170.15739756006474</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>-43.2210272293922,170.1578792332272</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>-43.22048210579205,170.15839704960104</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>-43.21999297910346,170.158994698847</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>-43.21947688070215,170.15966724020765</t>
+        </is>
+      </c>
+      <c r="R319" t="inlineStr">
+        <is>
+          <t>-43.22045118253032,170.1619658347002</t>
+        </is>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>-43.220331957511,170.16290291665953</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>-43.21817661038422,170.16190051732977</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>-43.21793782069267,170.1627695566485</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>-43.21708336697717,170.16303744065533</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>-43.21782396898805,170.16486282155566</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>-43.21737014172314,170.16551267670434</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>-43.216953819222184,170.16619938950876</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>-43.21647728208703,170.16683841989413</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>-43.215976343800335,170.16742173348376</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>-43.215473221487024,170.16800082359669</t>
+        </is>
+      </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-26 22:19:44+00:00</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>-43.226073077321374,170.1501666495356</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>-43.22592975338748,170.1510487994333</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>-43.225674865286585,170.15187811371476</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>-43.22538462164801,170.1526441637149</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>-43.225020552927504,170.15332312261108</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>-43.22457984030359,170.153983159875</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>-43.224092510380615,170.15460125988417</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>-43.22359038934343,170.1552036709321</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>-43.223053472568566,170.15570994162775</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>-43.22262948043834,170.1563040275216</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>-43.22212531571023,170.15685479160302</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>-43.22159770273849,170.15739756006474</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>-43.2210272293922,170.1578792332272</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>-43.22048210579205,170.15839704960104</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>-43.21999297910346,170.158994698847</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>-43.21947688070215,170.15966724020765</t>
+        </is>
+      </c>
+      <c r="R320" t="inlineStr">
+        <is>
+          <t>-43.22045118253032,170.1619658347002</t>
+        </is>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>-43.220331957511,170.16290291665953</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>-43.21817661038422,170.16190051732977</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>-43.21793782069267,170.1627695566485</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>-43.21708336697717,170.16303744065533</t>
+        </is>
+      </c>
+      <c r="W320" t="inlineStr">
+        <is>
+          <t>-43.21782396898805,170.16486282155566</t>
+        </is>
+      </c>
+      <c r="X320" t="inlineStr">
+        <is>
+          <t>-43.21737014172314,170.16551267670434</t>
+        </is>
+      </c>
+      <c r="Y320" t="inlineStr">
+        <is>
+          <t>-43.216953819222184,170.16619938950876</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>-43.21647728208703,170.16683841989413</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>-43.215976343800335,170.16742173348376</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>-43.215473221487024,170.16800082359669</t>
+        </is>
+      </c>
+      <c r="AC320" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0425/nzd0425.xlsx
+++ b/data/nzd0425/nzd0425.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC320"/>
+  <dimension ref="A1:AC321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29833,10 +29833,10 @@
         <v>285.02</v>
       </c>
       <c r="T318" t="n">
-        <v>415.81</v>
+        <v>376.68</v>
       </c>
       <c r="U318" t="n">
-        <v>392.31</v>
+        <v>371.47</v>
       </c>
       <c r="V318" t="n">
         <v>377.43</v>
@@ -29908,7 +29908,7 @@
         <v>428.67</v>
       </c>
       <c r="N319" t="n">
-        <v>442.81</v>
+        <v>430.7</v>
       </c>
       <c r="O319" t="n">
         <v>452.88</v>
@@ -29920,19 +29920,15 @@
         <v>452.95</v>
       </c>
       <c r="R319" t="n">
-        <v>249.09</v>
+        <v>338.31</v>
       </c>
       <c r="S319" t="n">
-        <v>214.19</v>
-      </c>
-      <c r="T319" t="n">
-        <v>454.95</v>
-      </c>
-      <c r="U319" t="n">
-        <v>434</v>
-      </c>
+        <v>291.39</v>
+      </c>
+      <c r="T319" t="inlineStr"/>
+      <c r="U319" t="inlineStr"/>
       <c r="V319" t="n">
-        <v>497.12</v>
+        <v>381.47</v>
       </c>
       <c r="W319" t="n">
         <v>342.43</v>
@@ -30001,7 +29997,7 @@
         <v>428.67</v>
       </c>
       <c r="N320" t="n">
-        <v>442.81</v>
+        <v>430.7</v>
       </c>
       <c r="O320" t="n">
         <v>452.88</v>
@@ -30013,19 +30009,15 @@
         <v>452.95</v>
       </c>
       <c r="R320" t="n">
-        <v>249.09</v>
+        <v>338.31</v>
       </c>
       <c r="S320" t="n">
-        <v>214.19</v>
-      </c>
-      <c r="T320" t="n">
-        <v>454.95</v>
-      </c>
-      <c r="U320" t="n">
-        <v>434</v>
-      </c>
+        <v>291.39</v>
+      </c>
+      <c r="T320" t="inlineStr"/>
+      <c r="U320" t="inlineStr"/>
       <c r="V320" t="n">
-        <v>497.12</v>
+        <v>381.47</v>
       </c>
       <c r="W320" t="n">
         <v>342.43</v>
@@ -30048,6 +30040,99 @@
       <c r="AC320" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:19:44+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>371.53</v>
+      </c>
+      <c r="C321" t="n">
+        <v>357.85</v>
+      </c>
+      <c r="D321" t="n">
+        <v>363.61</v>
+      </c>
+      <c r="E321" t="n">
+        <v>373.6</v>
+      </c>
+      <c r="F321" t="n">
+        <v>370.9</v>
+      </c>
+      <c r="G321" t="n">
+        <v>376.38</v>
+      </c>
+      <c r="H321" t="n">
+        <v>385.15</v>
+      </c>
+      <c r="I321" t="n">
+        <v>397.6</v>
+      </c>
+      <c r="J321" t="n">
+        <v>416.55</v>
+      </c>
+      <c r="K321" t="n">
+        <v>415.07</v>
+      </c>
+      <c r="L321" t="n">
+        <v>417.36</v>
+      </c>
+      <c r="M321" t="n">
+        <v>424.18</v>
+      </c>
+      <c r="N321" t="n">
+        <v>422.73</v>
+      </c>
+      <c r="O321" t="n">
+        <v>442.58</v>
+      </c>
+      <c r="P321" t="n">
+        <v>441.53</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>435.85</v>
+      </c>
+      <c r="R321" t="n">
+        <v>380.04</v>
+      </c>
+      <c r="S321" t="n">
+        <v>373.88</v>
+      </c>
+      <c r="T321" t="n">
+        <v>371.21</v>
+      </c>
+      <c r="U321" t="n">
+        <v>380.96</v>
+      </c>
+      <c r="V321" t="n">
+        <v>371.61</v>
+      </c>
+      <c r="W321" t="n">
+        <v>354.44</v>
+      </c>
+      <c r="X321" t="n">
+        <v>372.09</v>
+      </c>
+      <c r="Y321" t="n">
+        <v>364.15</v>
+      </c>
+      <c r="Z321" t="n">
+        <v>341.39</v>
+      </c>
+      <c r="AA321" t="n">
+        <v>335.59</v>
+      </c>
+      <c r="AB321" t="n">
+        <v>313.45</v>
+      </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -30062,7 +30147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B324"/>
+  <dimension ref="A1:B325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33305,6 +33390,16 @@
       </c>
       <c r="B324" t="n">
         <v>0.72</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>
@@ -33473,28 +33568,28 @@
         <v>0.1361</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7651263176104314</v>
+        <v>-0.7627998426748333</v>
       </c>
       <c r="J2" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K2" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2136528005275372</v>
+        <v>0.2137636238759407</v>
       </c>
       <c r="M2" t="n">
-        <v>8.427501731092294</v>
+        <v>8.413130114388116</v>
       </c>
       <c r="N2" t="n">
-        <v>120.5569535436073</v>
+        <v>120.2228559026329</v>
       </c>
       <c r="O2" t="n">
-        <v>10.97984305641967</v>
+        <v>10.96461836557173</v>
       </c>
       <c r="P2" t="n">
-        <v>388.2790610855527</v>
+        <v>388.2546507250455</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33551,28 +33646,28 @@
         <v>0.1113</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8097232088775621</v>
+        <v>-0.8137896829649504</v>
       </c>
       <c r="J3" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K3" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1490581610789882</v>
+        <v>0.1511631544638445</v>
       </c>
       <c r="M3" t="n">
-        <v>10.93849553050753</v>
+        <v>10.92388380084982</v>
       </c>
       <c r="N3" t="n">
-        <v>209.4293394706811</v>
+        <v>208.9051550712094</v>
       </c>
       <c r="O3" t="n">
-        <v>14.47167369279314</v>
+        <v>14.45355164211238</v>
       </c>
       <c r="P3" t="n">
-        <v>385.9896236862169</v>
+        <v>386.0322908548795</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33629,28 +33724,28 @@
         <v>0.1963</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6677475244621592</v>
+        <v>-0.671968169558012</v>
       </c>
       <c r="J4" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K4" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09985392553283967</v>
+        <v>0.1015820987485482</v>
       </c>
       <c r="M4" t="n">
-        <v>11.30850716512076</v>
+        <v>11.30121552796381</v>
       </c>
       <c r="N4" t="n">
-        <v>224.9016552602567</v>
+        <v>224.3391858443935</v>
       </c>
       <c r="O4" t="n">
-        <v>14.99672148371959</v>
+        <v>14.97795666452515</v>
       </c>
       <c r="P4" t="n">
-        <v>388.198772426297</v>
+        <v>388.2430572224864</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33707,28 +33802,28 @@
         <v>0.1229</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5882837233664682</v>
+        <v>-0.593965937573681</v>
       </c>
       <c r="J5" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K5" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05724147833193227</v>
+        <v>0.05863489087030804</v>
       </c>
       <c r="M5" t="n">
-        <v>14.26562341678412</v>
+        <v>14.25574506708542</v>
       </c>
       <c r="N5" t="n">
-        <v>318.9212956676512</v>
+        <v>318.1790475520414</v>
       </c>
       <c r="O5" t="n">
-        <v>17.85836766526133</v>
+        <v>17.8375740377452</v>
       </c>
       <c r="P5" t="n">
-        <v>398.4037524496577</v>
+        <v>398.4633726480767</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33785,28 +33880,28 @@
         <v>0.1248</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5104249995279964</v>
+        <v>-0.51511184105288</v>
       </c>
       <c r="J6" t="n">
+        <v>320</v>
+      </c>
+      <c r="K6" t="n">
         <v>319</v>
       </c>
-      <c r="K6" t="n">
-        <v>318</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03910792907586114</v>
+        <v>0.04005429855393328</v>
       </c>
       <c r="M6" t="n">
-        <v>14.93991409452051</v>
+        <v>14.92253387809084</v>
       </c>
       <c r="N6" t="n">
-        <v>357.8019815610132</v>
+        <v>356.8533375838801</v>
       </c>
       <c r="O6" t="n">
-        <v>18.91565440477842</v>
+        <v>18.8905621299071</v>
       </c>
       <c r="P6" t="n">
-        <v>392.0172254351936</v>
+        <v>392.0664970946434</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33863,28 +33958,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4192737202226078</v>
+        <v>-0.4185474630534919</v>
       </c>
       <c r="J7" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K7" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0275932440977239</v>
+        <v>0.02769068811596709</v>
       </c>
       <c r="M7" t="n">
-        <v>14.6873910019256</v>
+        <v>14.64420724227203</v>
       </c>
       <c r="N7" t="n">
-        <v>346.625666889415</v>
+        <v>345.5466172467089</v>
       </c>
       <c r="O7" t="n">
-        <v>18.61788567183221</v>
+        <v>18.58888423888612</v>
       </c>
       <c r="P7" t="n">
-        <v>386.4386963175983</v>
+        <v>386.4310761197411</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33941,28 +34036,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1250691165796506</v>
+        <v>-0.1214756845942125</v>
       </c>
       <c r="J8" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K8" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002187344900420829</v>
+        <v>0.002077868466364152</v>
       </c>
       <c r="M8" t="n">
-        <v>15.52835763176416</v>
+        <v>15.49129670796772</v>
       </c>
       <c r="N8" t="n">
-        <v>399.2566272978462</v>
+        <v>398.1106848273551</v>
       </c>
       <c r="O8" t="n">
-        <v>19.98140703999211</v>
+        <v>19.9527112149541</v>
       </c>
       <c r="P8" t="n">
-        <v>382.7622891272622</v>
+        <v>382.7245853167116</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34019,28 +34114,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1028641139818463</v>
+        <v>0.1108083010515918</v>
       </c>
       <c r="J9" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K9" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001368901311614268</v>
+        <v>0.001597621157770401</v>
       </c>
       <c r="M9" t="n">
-        <v>15.72070985806545</v>
+        <v>15.69828993510596</v>
       </c>
       <c r="N9" t="n">
-        <v>431.8977640103425</v>
+        <v>431.0453031413678</v>
       </c>
       <c r="O9" t="n">
-        <v>20.78215012962669</v>
+        <v>20.76163055112406</v>
       </c>
       <c r="P9" t="n">
-        <v>382.1679635700237</v>
+        <v>382.0846097941708</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34097,28 +34192,28 @@
         <v>0.1309</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4141919256858329</v>
+        <v>0.42811330283494</v>
       </c>
       <c r="J10" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K10" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02077072658120116</v>
+        <v>0.02223985464417011</v>
       </c>
       <c r="M10" t="n">
-        <v>16.57730392277556</v>
+        <v>16.58953021148983</v>
       </c>
       <c r="N10" t="n">
-        <v>452.5391799203917</v>
+        <v>452.6519060810832</v>
       </c>
       <c r="O10" t="n">
-        <v>21.2729682912468</v>
+        <v>21.27561764276382</v>
       </c>
       <c r="P10" t="n">
-        <v>383.2511636827699</v>
+        <v>383.105094696697</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34175,28 +34270,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7071725007039111</v>
+        <v>0.7192584743863171</v>
       </c>
       <c r="J11" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K11" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05963410091352539</v>
+        <v>0.06182334101488407</v>
       </c>
       <c r="M11" t="n">
-        <v>16.70357411590384</v>
+        <v>16.70130424403712</v>
       </c>
       <c r="N11" t="n">
-        <v>441.2382503839069</v>
+        <v>441.0102147387728</v>
       </c>
       <c r="O11" t="n">
-        <v>21.00567186223537</v>
+        <v>21.0002432066577</v>
       </c>
       <c r="P11" t="n">
-        <v>376.8741197315835</v>
+        <v>376.7473085761509</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34253,28 +34348,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9184473932663361</v>
+        <v>0.9313353391488002</v>
       </c>
       <c r="J12" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K12" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08487964278473792</v>
+        <v>0.08743023885970536</v>
       </c>
       <c r="M12" t="n">
-        <v>18.09334582319161</v>
+        <v>18.09011047731324</v>
       </c>
       <c r="N12" t="n">
-        <v>508.866047191839</v>
+        <v>508.5844704584888</v>
       </c>
       <c r="O12" t="n">
-        <v>22.55805947309828</v>
+        <v>22.55181745355546</v>
       </c>
       <c r="P12" t="n">
-        <v>372.2290104406195</v>
+        <v>372.0937846531525</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34331,28 +34426,28 @@
         <v>0.1835</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8114347424838836</v>
+        <v>0.8263978627109313</v>
       </c>
       <c r="J13" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K13" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0619083011444268</v>
+        <v>0.06430160282449371</v>
       </c>
       <c r="M13" t="n">
-        <v>18.75531391113129</v>
+        <v>18.75875816362022</v>
       </c>
       <c r="N13" t="n">
-        <v>558.2437032308336</v>
+        <v>558.2631717689917</v>
       </c>
       <c r="O13" t="n">
-        <v>23.62718144914525</v>
+        <v>23.62759344006477</v>
       </c>
       <c r="P13" t="n">
-        <v>378.5956553218941</v>
+        <v>378.4386559261706</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34409,28 +34504,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8075920513202618</v>
+        <v>0.8048834494103723</v>
       </c>
       <c r="J14" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K14" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06546895714306777</v>
+        <v>0.06595601384285721</v>
       </c>
       <c r="M14" t="n">
-        <v>18.75193958354734</v>
+        <v>18.68227206696834</v>
       </c>
       <c r="N14" t="n">
-        <v>520.9098985481032</v>
+        <v>515.3774870896634</v>
       </c>
       <c r="O14" t="n">
-        <v>22.82345062754761</v>
+        <v>22.70192694661983</v>
       </c>
       <c r="P14" t="n">
-        <v>381.3939721295873</v>
+        <v>381.4218767760392</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34487,28 +34582,28 @@
         <v>0.0862</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3666464168273637</v>
+        <v>0.3943210577593071</v>
       </c>
       <c r="J15" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K15" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L15" t="n">
-        <v>0.009278270759502272</v>
+        <v>0.01071452918067639</v>
       </c>
       <c r="M15" t="n">
-        <v>23.2037513874241</v>
+        <v>23.21849730787208</v>
       </c>
       <c r="N15" t="n">
-        <v>805.5074124393016</v>
+        <v>808.9174497524459</v>
       </c>
       <c r="O15" t="n">
-        <v>28.3814624788664</v>
+        <v>28.4414741135625</v>
       </c>
       <c r="P15" t="n">
-        <v>389.1148085189028</v>
+        <v>388.8257510264612</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34565,28 +34660,28 @@
         <v>0.08890000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3625828432279433</v>
+        <v>0.3957339864538135</v>
       </c>
       <c r="J16" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K16" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L16" t="n">
-        <v>0.003423492549534224</v>
+        <v>0.004088432083987459</v>
       </c>
       <c r="M16" t="n">
-        <v>31.47061420848349</v>
+        <v>31.43513597193271</v>
       </c>
       <c r="N16" t="n">
-        <v>2084.051021234047</v>
+        <v>2085.804382447187</v>
       </c>
       <c r="O16" t="n">
-        <v>45.65140765884495</v>
+        <v>45.67060742367224</v>
       </c>
       <c r="P16" t="n">
-        <v>380.1871357271554</v>
+        <v>379.8323110526345</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34643,28 +34738,28 @@
         <v>0.0687</v>
       </c>
       <c r="I17" t="n">
-        <v>0.679189088730121</v>
+        <v>0.7198031255529388</v>
       </c>
       <c r="J17" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K17" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01324983219463982</v>
+        <v>0.01487621584612564</v>
       </c>
       <c r="M17" t="n">
-        <v>31.03601404889949</v>
+        <v>31.06974369421473</v>
       </c>
       <c r="N17" t="n">
-        <v>1856.260053725682</v>
+        <v>1861.972210441553</v>
       </c>
       <c r="O17" t="n">
-        <v>43.08433652414392</v>
+        <v>43.15057601517682</v>
       </c>
       <c r="P17" t="n">
-        <v>357.2259460232734</v>
+        <v>356.7921217273852</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -34725,28 +34820,28 @@
         <v>0.0464</v>
       </c>
       <c r="I18" t="n">
-        <v>2.149128678937242</v>
+        <v>2.257369399156822</v>
       </c>
       <c r="J18" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K18" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1954074155487774</v>
+        <v>0.2318332533650794</v>
       </c>
       <c r="M18" t="n">
-        <v>24.43074842839059</v>
+        <v>23.76360441969506</v>
       </c>
       <c r="N18" t="n">
-        <v>1086.438986380565</v>
+        <v>968.3093957767911</v>
       </c>
       <c r="O18" t="n">
-        <v>32.96117392297436</v>
+        <v>31.11767015341591</v>
       </c>
       <c r="P18" t="n">
-        <v>332.0609341320369</v>
+        <v>330.9312230728437</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -34807,28 +34902,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7127597845348451</v>
+        <v>0.8144143387743705</v>
       </c>
       <c r="J19" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K19" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0143515687782626</v>
+        <v>0.01994430036875205</v>
       </c>
       <c r="M19" t="n">
-        <v>32.05776224759364</v>
+        <v>31.31588727857492</v>
       </c>
       <c r="N19" t="n">
-        <v>1977.361850608272</v>
+        <v>1854.58877385581</v>
       </c>
       <c r="O19" t="n">
-        <v>44.46753704229943</v>
+        <v>43.06493671022645</v>
       </c>
       <c r="P19" t="n">
-        <v>349.4788473585328</v>
+        <v>348.4222235990965</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -34889,28 +34984,28 @@
         <v>0.0269</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.02627706215553786</v>
+        <v>-0.1696729936907689</v>
       </c>
       <c r="J20" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K20" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L20" t="n">
-        <v>2.768007134579253e-05</v>
+        <v>0.001204483839016612</v>
       </c>
       <c r="M20" t="n">
-        <v>25.06395795586282</v>
+        <v>24.53141791053218</v>
       </c>
       <c r="N20" t="n">
-        <v>1448.079086247053</v>
+        <v>1380.540056460711</v>
       </c>
       <c r="O20" t="n">
-        <v>38.05363433690733</v>
+        <v>37.15561944660202</v>
       </c>
       <c r="P20" t="n">
-        <v>360.7355955358569</v>
+        <v>362.209931943553</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -34971,28 +35066,28 @@
         <v>0.0312</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.76667689402568</v>
+        <v>-0.8761992209184528</v>
       </c>
       <c r="J21" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K21" t="n">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01726356942736529</v>
+        <v>0.02300692353731448</v>
       </c>
       <c r="M21" t="n">
-        <v>30.44721498517852</v>
+        <v>30.10695842386726</v>
       </c>
       <c r="N21" t="n">
-        <v>1899.045296745189</v>
+        <v>1843.244561160703</v>
       </c>
       <c r="O21" t="n">
-        <v>43.57803686199263</v>
+        <v>42.93302413248691</v>
       </c>
       <c r="P21" t="n">
-        <v>357.3348643345932</v>
+        <v>358.4732401578096</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -35053,28 +35148,28 @@
         <v>0.0247</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8605949570779163</v>
+        <v>0.7121846234111988</v>
       </c>
       <c r="J22" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K22" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="L22" t="n">
-        <v>0.05308590074417752</v>
+        <v>0.042655888339038</v>
       </c>
       <c r="M22" t="n">
-        <v>19.77939653984897</v>
+        <v>19.04983140016595</v>
       </c>
       <c r="N22" t="n">
-        <v>743.0802133931752</v>
+        <v>642.895865432276</v>
       </c>
       <c r="O22" t="n">
-        <v>27.25949767316293</v>
+        <v>25.35539124983632</v>
       </c>
       <c r="P22" t="n">
-        <v>351.3697513734327</v>
+        <v>352.9163001929161</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -35135,28 +35230,28 @@
         <v>0.0528</v>
       </c>
       <c r="I23" t="n">
-        <v>1.164461740646493</v>
+        <v>1.155737861693003</v>
       </c>
       <c r="J23" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K23" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1625267818232569</v>
+        <v>0.1612400215454045</v>
       </c>
       <c r="M23" t="n">
-        <v>15.19996657426504</v>
+        <v>15.20622730431909</v>
       </c>
       <c r="N23" t="n">
-        <v>392.0926424989547</v>
+        <v>391.461805009303</v>
       </c>
       <c r="O23" t="n">
-        <v>19.80132931141126</v>
+        <v>19.78539372894315</v>
       </c>
       <c r="P23" t="n">
-        <v>337.2106769588792</v>
+        <v>337.3022138143163</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -35213,28 +35308,28 @@
         <v>0.0794</v>
       </c>
       <c r="I24" t="n">
-        <v>1.129102736857184</v>
+        <v>1.132851454488867</v>
       </c>
       <c r="J24" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K24" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1348233971624708</v>
+        <v>0.1364037646732911</v>
       </c>
       <c r="M24" t="n">
-        <v>16.67490126879613</v>
+        <v>16.64305218500049</v>
       </c>
       <c r="N24" t="n">
-        <v>456.8215456826809</v>
+        <v>455.4956331882062</v>
       </c>
       <c r="O24" t="n">
-        <v>21.37338404845337</v>
+        <v>21.34234366671585</v>
       </c>
       <c r="P24" t="n">
-        <v>335.9288525370008</v>
+        <v>335.8893682176473</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -35291,28 +35386,28 @@
         <v>0.1141</v>
       </c>
       <c r="I25" t="n">
-        <v>1.090777972399203</v>
+        <v>1.100143845734769</v>
       </c>
       <c r="J25" t="n">
+        <v>320</v>
+      </c>
+      <c r="K25" t="n">
         <v>319</v>
       </c>
-      <c r="K25" t="n">
-        <v>318</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.1353589062444259</v>
+        <v>0.1380214477765185</v>
       </c>
       <c r="M25" t="n">
-        <v>15.90167731042217</v>
+        <v>15.90514515469718</v>
       </c>
       <c r="N25" t="n">
-        <v>426.0813031869384</v>
+        <v>425.4390314691783</v>
       </c>
       <c r="O25" t="n">
-        <v>20.64173692272379</v>
+        <v>20.62617345678006</v>
       </c>
       <c r="P25" t="n">
-        <v>320.0266503951221</v>
+        <v>319.9283949655358</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -35369,28 +35464,28 @@
         <v>0.2</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9397476851348782</v>
+        <v>0.9493942856734063</v>
       </c>
       <c r="J26" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K26" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1190731594870237</v>
+        <v>0.121776264131637</v>
       </c>
       <c r="M26" t="n">
-        <v>15.05714690010798</v>
+        <v>15.05522335936561</v>
       </c>
       <c r="N26" t="n">
-        <v>365.5684638989624</v>
+        <v>365.1592210658365</v>
       </c>
       <c r="O26" t="n">
-        <v>19.11984476660212</v>
+        <v>19.10913972594885</v>
       </c>
       <c r="P26" t="n">
-        <v>300.8590952070771</v>
+        <v>300.757878987976</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -35447,28 +35542,28 @@
         <v>0.2</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8856811523424412</v>
+        <v>0.9008311011635057</v>
       </c>
       <c r="J27" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K27" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1245705607128158</v>
+        <v>0.1284560311087646</v>
       </c>
       <c r="M27" t="n">
-        <v>13.86271311918492</v>
+        <v>13.8900190604967</v>
       </c>
       <c r="N27" t="n">
-        <v>308.4471508739169</v>
+        <v>309.2915585335113</v>
       </c>
       <c r="O27" t="n">
-        <v>17.56266354725037</v>
+        <v>17.58668696865647</v>
       </c>
       <c r="P27" t="n">
-        <v>287.7285549744644</v>
+        <v>287.5695952939927</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -35525,28 +35620,28 @@
         <v>0.121</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9099626939368448</v>
+        <v>0.9168396542865075</v>
       </c>
       <c r="J28" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K28" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1508087971056146</v>
+        <v>0.1534830042586304</v>
       </c>
       <c r="M28" t="n">
-        <v>12.89281836942874</v>
+        <v>12.88741183508755</v>
       </c>
       <c r="N28" t="n">
-        <v>260.8832617186483</v>
+        <v>260.4406011339353</v>
       </c>
       <c r="O28" t="n">
-        <v>16.15188105821264</v>
+        <v>16.138172174504</v>
       </c>
       <c r="P28" t="n">
-        <v>278.1358809703003</v>
+        <v>278.0637249892663</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -35584,7 +35679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC320"/>
+  <dimension ref="A1:AC321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81896,12 +81991,12 @@
       </c>
       <c r="T318" t="inlineStr">
         <is>
-          <t>-43.218463241750726,170.1621803945162</t>
+          <t>-43.218749799260785,170.16246020278572</t>
         </is>
       </c>
       <c r="U318" t="inlineStr">
         <is>
-          <t>-43.21824312473553,170.16306767030449</t>
+          <t>-43.21839573987541,170.16321669248077</t>
         </is>
       </c>
       <c r="V318" t="inlineStr">
@@ -82013,7 +82108,7 @@
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>-43.2210272293922,170.1578792332272</t>
+          <t>-43.22110266512886,170.15798677243964</t>
         </is>
       </c>
       <c r="O319" t="inlineStr">
@@ -82033,27 +82128,19 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>-43.22045118253032,170.1619658347002</t>
+          <t>-43.219813738444586,170.16129837491957</t>
         </is>
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>-43.220331957511,170.16290291665953</t>
-        </is>
-      </c>
-      <c r="T319" t="inlineStr">
-        <is>
-          <t>-43.21817661038422,170.16190051732977</t>
-        </is>
-      </c>
-      <c r="U319" t="inlineStr">
-        <is>
-          <t>-43.21793782069267,170.1627695566485</t>
-        </is>
-      </c>
+          <t>-43.219766607408296,170.16235086245976</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr"/>
+      <c r="U319" t="inlineStr"/>
       <c r="V319" t="inlineStr">
         <is>
-          <t>-43.21708336697717,170.16303744065533</t>
+          <t>-43.2179302925247,170.16386441862915</t>
         </is>
       </c>
       <c r="W319" t="inlineStr">
@@ -82160,7 +82247,7 @@
       </c>
       <c r="N320" t="inlineStr">
         <is>
-          <t>-43.2210272293922,170.1578792332272</t>
+          <t>-43.22110266512886,170.15798677243964</t>
         </is>
       </c>
       <c r="O320" t="inlineStr">
@@ -82180,27 +82267,19 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>-43.22045118253032,170.1619658347002</t>
+          <t>-43.219813738444586,170.16129837491957</t>
         </is>
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>-43.220331957511,170.16290291665953</t>
-        </is>
-      </c>
-      <c r="T320" t="inlineStr">
-        <is>
-          <t>-43.21817661038422,170.16190051732977</t>
-        </is>
-      </c>
-      <c r="U320" t="inlineStr">
-        <is>
-          <t>-43.21793782069267,170.1627695566485</t>
-        </is>
-      </c>
+          <t>-43.219766607408296,170.16235086245976</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr"/>
+      <c r="U320" t="inlineStr"/>
       <c r="V320" t="inlineStr">
         <is>
-          <t>-43.21708336697717,170.16303744065533</t>
+          <t>-43.2179302925247,170.16386441862915</t>
         </is>
       </c>
       <c r="W320" t="inlineStr">
@@ -82236,6 +82315,153 @@
       <c r="AC320" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-19 22:19:44+00:00</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>-43.226049778251316,170.15015561537714</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>-43.22593800158077,170.15105270576362</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>-43.22566091991418,170.1518715090956</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>-43.2253611070687,170.15262758327273</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>-43.225011889660784,170.15331430723745</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>-43.22456291828205,170.15396520801826</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>-43.22408788883645,170.1545963570716</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>-43.223586692120485,170.15519974868897</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>-43.22306041713899,170.15571814885251</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>-43.22263825630287,170.1563160421714</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>-43.222150544220376,170.15689075672873</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>-43.22162567200348,170.15743743234935</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>-43.22115231188328,170.15805754777244</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>-43.22054626640825,170.1584885152046</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>-43.220070407496536,170.15910507888822</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>-43.21958981348057,170.15981016127898</t>
+        </is>
+      </c>
+      <c r="R321" t="inlineStr">
+        <is>
+          <t>-43.21951559171718,170.16098619519929</t>
+        </is>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>-43.21916251495728,170.16176099081497</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>-43.218789857212094,170.16249931751372</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>-43.21832624288789,170.16314883152344</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>-43.21800249880861,170.16393492553652</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
+        <is>
+          <t>-43.217736018407194,170.16477693965265</t>
+        </is>
+      </c>
+      <c r="X321" t="inlineStr">
+        <is>
+          <t>-43.217230245702076,170.16534172180454</t>
+        </is>
+      </c>
+      <c r="Y321" t="inlineStr">
+        <is>
+          <t>-43.216812542619756,170.16595669248957</t>
+        </is>
+      </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t>-43.21639485568873,170.16667866089736</t>
+        </is>
+      </c>
+      <c r="AA321" t="inlineStr">
+        <is>
+          <t>-43.215881727877246,170.167238348254</t>
+        </is>
+      </c>
+      <c r="AB321" t="inlineStr">
+        <is>
+          <t>-43.21545335438229,170.16796231683642</t>
+        </is>
+      </c>
+      <c r="AC321" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0425/nzd0425.xlsx
+++ b/data/nzd0425/nzd0425.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC321"/>
+  <dimension ref="A1:AC323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30113,13 +30113,13 @@
         <v>371.61</v>
       </c>
       <c r="W321" t="n">
-        <v>354.44</v>
+        <v>328.51</v>
       </c>
       <c r="X321" t="n">
-        <v>372.09</v>
+        <v>345.01</v>
       </c>
       <c r="Y321" t="n">
-        <v>364.15</v>
+        <v>334.28</v>
       </c>
       <c r="Z321" t="n">
         <v>341.39</v>
@@ -30133,6 +30133,192 @@
       <c r="AC321" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:19:57+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>369.24</v>
+      </c>
+      <c r="C322" t="n">
+        <v>354.92</v>
+      </c>
+      <c r="D322" t="n">
+        <v>359.95</v>
+      </c>
+      <c r="E322" t="n">
+        <v>372.91</v>
+      </c>
+      <c r="F322" t="n">
+        <v>370.13</v>
+      </c>
+      <c r="G322" t="n">
+        <v>372.99</v>
+      </c>
+      <c r="H322" t="n">
+        <v>379.93</v>
+      </c>
+      <c r="I322" t="n">
+        <v>390.7</v>
+      </c>
+      <c r="J322" t="n">
+        <v>410.45</v>
+      </c>
+      <c r="K322" t="n">
+        <v>403.25</v>
+      </c>
+      <c r="L322" t="n">
+        <v>398.97</v>
+      </c>
+      <c r="M322" t="n">
+        <v>402.47</v>
+      </c>
+      <c r="N322" t="n">
+        <v>404.25</v>
+      </c>
+      <c r="O322" t="n">
+        <v>423</v>
+      </c>
+      <c r="P322" t="n">
+        <v>421.23</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>412.27</v>
+      </c>
+      <c r="R322" t="n">
+        <v>387.35</v>
+      </c>
+      <c r="S322" t="n">
+        <v>389.21</v>
+      </c>
+      <c r="T322" t="n">
+        <v>389.09</v>
+      </c>
+      <c r="U322" t="n">
+        <v>341.66</v>
+      </c>
+      <c r="V322" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="W322" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="X322" t="n">
+        <v>349.17</v>
+      </c>
+      <c r="Y322" t="n">
+        <v>352.83</v>
+      </c>
+      <c r="Z322" t="n">
+        <v>355.09</v>
+      </c>
+      <c r="AA322" t="n">
+        <v>345.68</v>
+      </c>
+      <c r="AB322" t="n">
+        <v>322.84</v>
+      </c>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:04+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>372.52</v>
+      </c>
+      <c r="C323" t="n">
+        <v>352.98</v>
+      </c>
+      <c r="D323" t="n">
+        <v>356.67</v>
+      </c>
+      <c r="E323" t="n">
+        <v>367.77</v>
+      </c>
+      <c r="F323" t="n">
+        <v>365.81</v>
+      </c>
+      <c r="G323" t="n">
+        <v>370.27</v>
+      </c>
+      <c r="H323" t="n">
+        <v>377.34</v>
+      </c>
+      <c r="I323" t="n">
+        <v>389.45</v>
+      </c>
+      <c r="J323" t="n">
+        <v>406.22</v>
+      </c>
+      <c r="K323" t="n">
+        <v>397.13</v>
+      </c>
+      <c r="L323" t="n">
+        <v>394.87</v>
+      </c>
+      <c r="M323" t="n">
+        <v>400.93</v>
+      </c>
+      <c r="N323" t="n">
+        <v>404.63</v>
+      </c>
+      <c r="O323" t="n">
+        <v>424.69</v>
+      </c>
+      <c r="P323" t="n">
+        <v>419.3</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>411.09</v>
+      </c>
+      <c r="R323" t="n">
+        <v>395.67</v>
+      </c>
+      <c r="S323" t="n">
+        <v>397.82</v>
+      </c>
+      <c r="T323" t="n">
+        <v>398.72</v>
+      </c>
+      <c r="U323" t="n">
+        <v>333.51</v>
+      </c>
+      <c r="V323" t="n">
+        <v>221.34</v>
+      </c>
+      <c r="W323" t="n">
+        <v>166.91</v>
+      </c>
+      <c r="X323" t="n">
+        <v>367.2</v>
+      </c>
+      <c r="Y323" t="n">
+        <v>362.76</v>
+      </c>
+      <c r="Z323" t="n">
+        <v>356.11</v>
+      </c>
+      <c r="AA323" t="n">
+        <v>344.24</v>
+      </c>
+      <c r="AB323" t="n">
+        <v>325.39</v>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -30147,7 +30333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B325"/>
+  <dimension ref="A1:B327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33400,6 +33586,26 @@
       </c>
       <c r="B325" t="n">
         <v>-0.66</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -33568,28 +33774,28 @@
         <v>0.1361</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7627998426748333</v>
+        <v>-0.758970658814334</v>
       </c>
       <c r="J2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2137636238759407</v>
+        <v>0.2143444045816211</v>
       </c>
       <c r="M2" t="n">
-        <v>8.413130114388116</v>
+        <v>8.380265846436233</v>
       </c>
       <c r="N2" t="n">
-        <v>120.2228559026329</v>
+        <v>119.5512644529081</v>
       </c>
       <c r="O2" t="n">
-        <v>10.96461836557173</v>
+        <v>10.93395008461755</v>
       </c>
       <c r="P2" t="n">
-        <v>388.2546507250455</v>
+        <v>388.2143059661776</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -33646,28 +33852,28 @@
         <v>0.1113</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8137896829649504</v>
+        <v>-0.8264745280706508</v>
       </c>
       <c r="J3" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K3" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1511631544638445</v>
+        <v>0.1566288190736117</v>
       </c>
       <c r="M3" t="n">
-        <v>10.92388380084982</v>
+        <v>10.916462097124</v>
       </c>
       <c r="N3" t="n">
-        <v>208.9051550712094</v>
+        <v>208.2524755355381</v>
       </c>
       <c r="O3" t="n">
-        <v>14.45355164211238</v>
+        <v>14.43095546162963</v>
       </c>
       <c r="P3" t="n">
-        <v>386.0322908548795</v>
+        <v>386.1658853502578</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33724,28 +33930,28 @@
         <v>0.1963</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.671968169558012</v>
+        <v>-0.686700705394773</v>
       </c>
       <c r="J4" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K4" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1015820987485482</v>
+        <v>0.1065781941146374</v>
       </c>
       <c r="M4" t="n">
-        <v>11.30121552796381</v>
+        <v>11.3282869358644</v>
       </c>
       <c r="N4" t="n">
-        <v>224.3391858443935</v>
+        <v>223.8243445105194</v>
       </c>
       <c r="O4" t="n">
-        <v>14.97795666452515</v>
+        <v>14.96076015817777</v>
       </c>
       <c r="P4" t="n">
-        <v>388.2430572224864</v>
+        <v>388.3982239272526</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33802,28 +34008,28 @@
         <v>0.1229</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.593965937573681</v>
+        <v>-0.6090508362075202</v>
       </c>
       <c r="J5" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K5" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05863489087030804</v>
+        <v>0.0621128008151407</v>
       </c>
       <c r="M5" t="n">
-        <v>14.25574506708542</v>
+        <v>14.25907155693113</v>
       </c>
       <c r="N5" t="n">
-        <v>318.1790475520414</v>
+        <v>317.1470866269138</v>
       </c>
       <c r="O5" t="n">
-        <v>17.8375740377452</v>
+        <v>17.80862393973532</v>
       </c>
       <c r="P5" t="n">
-        <v>398.4633726480767</v>
+        <v>398.6222613196714</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33880,28 +34086,28 @@
         <v>0.1248</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.51511184105288</v>
+        <v>-0.5278575476181959</v>
       </c>
       <c r="J6" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K6" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04005429855393328</v>
+        <v>0.04247173577167906</v>
       </c>
       <c r="M6" t="n">
-        <v>14.92253387809084</v>
+        <v>14.90861096580511</v>
       </c>
       <c r="N6" t="n">
-        <v>356.8533375838801</v>
+        <v>355.3036035685565</v>
       </c>
       <c r="O6" t="n">
-        <v>18.8905621299071</v>
+        <v>18.84949876173254</v>
       </c>
       <c r="P6" t="n">
-        <v>392.0664970946434</v>
+        <v>392.2010082539151</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33958,28 +34164,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4185474630534919</v>
+        <v>-0.4229671887591628</v>
       </c>
       <c r="J7" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K7" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02769068811596709</v>
+        <v>0.02864587034245503</v>
       </c>
       <c r="M7" t="n">
-        <v>14.64420724227203</v>
+        <v>14.58043821306418</v>
       </c>
       <c r="N7" t="n">
-        <v>345.5466172467089</v>
+        <v>343.489186776397</v>
       </c>
       <c r="O7" t="n">
-        <v>18.58888423888612</v>
+        <v>18.53346127350196</v>
       </c>
       <c r="P7" t="n">
-        <v>386.4310761197411</v>
+        <v>386.4776361522148</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34036,28 +34242,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1214756845942125</v>
+        <v>-0.1225059042921546</v>
       </c>
       <c r="J8" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K8" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002077868466364152</v>
+        <v>0.002143149456609428</v>
       </c>
       <c r="M8" t="n">
-        <v>15.49129670796772</v>
+        <v>15.40494754234531</v>
       </c>
       <c r="N8" t="n">
-        <v>398.1106848273551</v>
+        <v>395.6525498579838</v>
       </c>
       <c r="O8" t="n">
-        <v>19.9527112149541</v>
+        <v>19.89101681307378</v>
       </c>
       <c r="P8" t="n">
-        <v>382.7245853167116</v>
+        <v>382.7354500876303</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34114,28 +34320,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1108083010515918</v>
+        <v>0.1170141514484516</v>
       </c>
       <c r="J9" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K9" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001597621157770401</v>
+        <v>0.001805931031817698</v>
       </c>
       <c r="M9" t="n">
-        <v>15.69828993510596</v>
+        <v>15.62186423262711</v>
       </c>
       <c r="N9" t="n">
-        <v>431.0453031413678</v>
+        <v>428.5235981726431</v>
       </c>
       <c r="O9" t="n">
-        <v>20.76163055112406</v>
+        <v>20.70081153415593</v>
       </c>
       <c r="P9" t="n">
-        <v>382.0846097941708</v>
+        <v>382.0192640756915</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34192,28 +34398,28 @@
         <v>0.1309</v>
       </c>
       <c r="I10" t="n">
-        <v>0.42811330283494</v>
+        <v>0.4451201574689208</v>
       </c>
       <c r="J10" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K10" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02223985464417011</v>
+        <v>0.02427021993023515</v>
       </c>
       <c r="M10" t="n">
-        <v>16.58953021148983</v>
+        <v>16.56442551895561</v>
       </c>
       <c r="N10" t="n">
-        <v>452.6519060810832</v>
+        <v>451.0186654870745</v>
       </c>
       <c r="O10" t="n">
-        <v>21.27561764276382</v>
+        <v>21.23720003877805</v>
       </c>
       <c r="P10" t="n">
-        <v>383.105094696697</v>
+        <v>382.9260225308815</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34270,28 +34476,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7192584743863171</v>
+        <v>0.7243750867476589</v>
       </c>
       <c r="J11" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K11" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06182334101488407</v>
+        <v>0.06346453178758127</v>
       </c>
       <c r="M11" t="n">
-        <v>16.70130424403712</v>
+        <v>16.61844944830608</v>
       </c>
       <c r="N11" t="n">
-        <v>441.0102147387728</v>
+        <v>438.4340780306552</v>
       </c>
       <c r="O11" t="n">
-        <v>21.0002432066577</v>
+        <v>20.93881749360873</v>
       </c>
       <c r="P11" t="n">
-        <v>376.7473085761509</v>
+        <v>376.6934630295233</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34348,28 +34554,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9313353391488002</v>
+        <v>0.9311278733658676</v>
       </c>
       <c r="J12" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K12" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L12" t="n">
-        <v>0.08743023885970536</v>
+        <v>0.08852525603365602</v>
       </c>
       <c r="M12" t="n">
-        <v>18.09011047731324</v>
+        <v>17.99077943161324</v>
       </c>
       <c r="N12" t="n">
-        <v>508.5844704584888</v>
+        <v>505.4523802491462</v>
       </c>
       <c r="O12" t="n">
-        <v>22.55181745355546</v>
+        <v>22.48226812955371</v>
       </c>
       <c r="P12" t="n">
-        <v>372.0937846531525</v>
+        <v>372.0959944418379</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34426,28 +34632,28 @@
         <v>0.1835</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8263978627109313</v>
+        <v>0.8277442408166749</v>
       </c>
       <c r="J13" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K13" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06430160282449371</v>
+        <v>0.06535536504722983</v>
       </c>
       <c r="M13" t="n">
-        <v>18.75875816362022</v>
+        <v>18.6477568264618</v>
       </c>
       <c r="N13" t="n">
-        <v>558.2631717689917</v>
+        <v>554.8067693709153</v>
       </c>
       <c r="O13" t="n">
-        <v>23.62759344006477</v>
+        <v>23.55433653005143</v>
       </c>
       <c r="P13" t="n">
-        <v>378.4386559261706</v>
+        <v>378.4244868189747</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34504,28 +34710,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8048834494103723</v>
+        <v>0.8066426882777951</v>
       </c>
       <c r="J14" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K14" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06595601384285721</v>
+        <v>0.0671041785268075</v>
       </c>
       <c r="M14" t="n">
-        <v>18.68227206696834</v>
+        <v>18.57302028724575</v>
       </c>
       <c r="N14" t="n">
-        <v>515.3774870896634</v>
+        <v>512.1888618866803</v>
       </c>
       <c r="O14" t="n">
-        <v>22.70192694661983</v>
+        <v>22.63158991071287</v>
       </c>
       <c r="P14" t="n">
-        <v>381.4218767760392</v>
+        <v>381.4033483103498</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34582,28 +34788,28 @@
         <v>0.0862</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3943210577593071</v>
+        <v>0.4249050979983801</v>
       </c>
       <c r="J15" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K15" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01071452918067639</v>
+        <v>0.01254067010151438</v>
       </c>
       <c r="M15" t="n">
-        <v>23.21849730787208</v>
+        <v>23.16856068868835</v>
       </c>
       <c r="N15" t="n">
-        <v>808.9174497524459</v>
+        <v>807.5179303622892</v>
       </c>
       <c r="O15" t="n">
-        <v>28.4414741135625</v>
+        <v>28.41685996661646</v>
       </c>
       <c r="P15" t="n">
-        <v>388.8257510264612</v>
+        <v>388.5051264053866</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -34660,28 +34866,28 @@
         <v>0.08890000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3957339864538135</v>
+        <v>0.4335186613299681</v>
       </c>
       <c r="J16" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K16" t="n">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L16" t="n">
-        <v>0.004088432083987459</v>
+        <v>0.004959739859124457</v>
       </c>
       <c r="M16" t="n">
-        <v>31.43513597193271</v>
+        <v>31.30933554304476</v>
       </c>
       <c r="N16" t="n">
-        <v>2085.804382447187</v>
+        <v>2078.191824245955</v>
       </c>
       <c r="O16" t="n">
-        <v>45.67060742367224</v>
+        <v>45.58718925582005</v>
       </c>
       <c r="P16" t="n">
-        <v>379.8323110526345</v>
+        <v>379.4264537472906</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -34738,28 +34944,28 @@
         <v>0.0687</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7198031255529388</v>
+        <v>0.7669472099846727</v>
       </c>
       <c r="J17" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K17" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01487621584612564</v>
+        <v>0.01703462436110514</v>
       </c>
       <c r="M17" t="n">
-        <v>31.06974369421473</v>
+        <v>31.02336782461665</v>
       </c>
       <c r="N17" t="n">
-        <v>1861.972210441553</v>
+        <v>1857.95383246539</v>
       </c>
       <c r="O17" t="n">
-        <v>43.15057601517682</v>
+        <v>43.10398859114305</v>
       </c>
       <c r="P17" t="n">
-        <v>356.7921217273852</v>
+        <v>356.2867894643949</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -34820,28 +35026,28 @@
         <v>0.0464</v>
       </c>
       <c r="I18" t="n">
-        <v>2.257369399156822</v>
+        <v>2.25739110949566</v>
       </c>
       <c r="J18" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K18" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2318332533650794</v>
+        <v>0.2343826592585174</v>
       </c>
       <c r="M18" t="n">
-        <v>23.76360441969506</v>
+        <v>23.63347155595879</v>
       </c>
       <c r="N18" t="n">
-        <v>968.3093957767911</v>
+        <v>962.0087859730802</v>
       </c>
       <c r="O18" t="n">
-        <v>31.11767015341591</v>
+        <v>31.01626647378888</v>
       </c>
       <c r="P18" t="n">
-        <v>330.9312230728437</v>
+        <v>330.9309411126412</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -34902,28 +35108,28 @@
         <v>0.0321</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8144143387743705</v>
+        <v>0.8438115389878197</v>
       </c>
       <c r="J19" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K19" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01994430036875205</v>
+        <v>0.02164292608509366</v>
       </c>
       <c r="M19" t="n">
-        <v>31.31588727857492</v>
+        <v>31.21815917029918</v>
       </c>
       <c r="N19" t="n">
-        <v>1854.58877385581</v>
+        <v>1846.181538558757</v>
       </c>
       <c r="O19" t="n">
-        <v>43.06493671022645</v>
+        <v>42.96721469398217</v>
       </c>
       <c r="P19" t="n">
-        <v>348.4222235990965</v>
+        <v>348.1144784518454</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -34984,28 +35190,28 @@
         <v>0.0269</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1696729936907689</v>
+        <v>-0.1220822966227327</v>
       </c>
       <c r="J20" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K20" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L20" t="n">
-        <v>0.001204483839016612</v>
+        <v>0.0006292999480109751</v>
       </c>
       <c r="M20" t="n">
-        <v>24.53141791053218</v>
+        <v>24.56149838712842</v>
       </c>
       <c r="N20" t="n">
-        <v>1380.540056460711</v>
+        <v>1380.053133197922</v>
       </c>
       <c r="O20" t="n">
-        <v>37.15561944660202</v>
+        <v>37.14906638393382</v>
       </c>
       <c r="P20" t="n">
-        <v>362.209931943553</v>
+        <v>361.7160133290336</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -35066,28 +35272,28 @@
         <v>0.0312</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8761992209184528</v>
+        <v>-0.8728571829698011</v>
       </c>
       <c r="J21" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K21" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L21" t="n">
-        <v>0.02300692353731448</v>
+        <v>0.02316294505716643</v>
       </c>
       <c r="M21" t="n">
-        <v>30.10695842386726</v>
+        <v>29.93538528716444</v>
       </c>
       <c r="N21" t="n">
-        <v>1843.244561160703</v>
+        <v>1831.502431167896</v>
       </c>
       <c r="O21" t="n">
-        <v>42.93302413248691</v>
+        <v>42.79605625718211</v>
       </c>
       <c r="P21" t="n">
-        <v>358.4732401578096</v>
+        <v>358.4382378517881</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -35148,28 +35354,28 @@
         <v>0.0247</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7121846234111988</v>
+        <v>0.5459553096063255</v>
       </c>
       <c r="J22" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K22" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L22" t="n">
-        <v>0.042655888339038</v>
+        <v>0.02214846378025837</v>
       </c>
       <c r="M22" t="n">
-        <v>19.04983140016595</v>
+        <v>19.9528594869394</v>
       </c>
       <c r="N22" t="n">
-        <v>642.895865432276</v>
+        <v>749.2234861747264</v>
       </c>
       <c r="O22" t="n">
-        <v>25.35539124983632</v>
+        <v>27.37194706583232</v>
       </c>
       <c r="P22" t="n">
-        <v>352.9163001929161</v>
+        <v>354.6608016115192</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -35230,28 +35436,28 @@
         <v>0.0528</v>
       </c>
       <c r="I23" t="n">
-        <v>1.155737861693003</v>
+        <v>0.9142415483782034</v>
       </c>
       <c r="J23" t="n">
+        <v>322</v>
+      </c>
+      <c r="K23" t="n">
         <v>320</v>
       </c>
-      <c r="K23" t="n">
-        <v>318</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.1612400215454045</v>
+        <v>0.0735247215156648</v>
       </c>
       <c r="M23" t="n">
-        <v>15.20622730431909</v>
+        <v>16.74263134778218</v>
       </c>
       <c r="N23" t="n">
-        <v>391.461805009303</v>
+        <v>598.0542981321069</v>
       </c>
       <c r="O23" t="n">
-        <v>19.78539372894315</v>
+        <v>24.4551487039459</v>
       </c>
       <c r="P23" t="n">
-        <v>337.3022138143163</v>
+        <v>339.8451287059481</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -35308,28 +35514,28 @@
         <v>0.0794</v>
       </c>
       <c r="I24" t="n">
-        <v>1.132851454488867</v>
+        <v>1.106134003221649</v>
       </c>
       <c r="J24" t="n">
+        <v>322</v>
+      </c>
+      <c r="K24" t="n">
         <v>320</v>
       </c>
-      <c r="K24" t="n">
-        <v>318</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.1364037646732911</v>
+        <v>0.1319498092901737</v>
       </c>
       <c r="M24" t="n">
-        <v>16.64305218500049</v>
+        <v>16.63279277530073</v>
       </c>
       <c r="N24" t="n">
-        <v>455.4956331882062</v>
+        <v>454.7978014898403</v>
       </c>
       <c r="O24" t="n">
-        <v>21.34234366671585</v>
+        <v>21.32598887484096</v>
       </c>
       <c r="P24" t="n">
-        <v>335.8893682176473</v>
+        <v>336.1710428285721</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -35386,28 +35592,28 @@
         <v>0.1141</v>
       </c>
       <c r="I25" t="n">
-        <v>1.100143845734769</v>
+        <v>1.092149992974881</v>
       </c>
       <c r="J25" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K25" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L25" t="n">
-        <v>0.1380214477765185</v>
+        <v>0.1377965493393951</v>
       </c>
       <c r="M25" t="n">
-        <v>15.90514515469718</v>
+        <v>15.85336353478547</v>
       </c>
       <c r="N25" t="n">
-        <v>425.4390314691783</v>
+        <v>423.394526466369</v>
       </c>
       <c r="O25" t="n">
-        <v>20.62617345678006</v>
+        <v>20.57655283244424</v>
       </c>
       <c r="P25" t="n">
-        <v>319.9283949655358</v>
+        <v>320.011782530738</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -35464,28 +35670,28 @@
         <v>0.2</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9493942856734063</v>
+        <v>0.9857326007886724</v>
       </c>
       <c r="J26" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K26" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L26" t="n">
-        <v>0.121776264131637</v>
+        <v>0.130016861246773</v>
       </c>
       <c r="M26" t="n">
-        <v>15.05522335936561</v>
+        <v>15.13393616729764</v>
       </c>
       <c r="N26" t="n">
-        <v>365.1592210658365</v>
+        <v>368.1404522791172</v>
       </c>
       <c r="O26" t="n">
-        <v>19.10913972594885</v>
+        <v>19.18698653460509</v>
       </c>
       <c r="P26" t="n">
-        <v>300.757878987976</v>
+        <v>300.3751973076871</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -35542,28 +35748,28 @@
         <v>0.2</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9008311011635057</v>
+        <v>0.9419393999666164</v>
       </c>
       <c r="J27" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K27" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1284560311087646</v>
+        <v>0.1378912661551889</v>
       </c>
       <c r="M27" t="n">
-        <v>13.8900190604967</v>
+        <v>14.00457504471909</v>
       </c>
       <c r="N27" t="n">
-        <v>309.2915585335113</v>
+        <v>314.0909008168611</v>
       </c>
       <c r="O27" t="n">
-        <v>17.58668696865647</v>
+        <v>17.7226098759991</v>
       </c>
       <c r="P27" t="n">
-        <v>287.5695952939927</v>
+        <v>287.1366961408406</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -35620,28 +35826,28 @@
         <v>0.121</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9168396542865075</v>
+        <v>0.9433908055164488</v>
       </c>
       <c r="J28" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K28" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L28" t="n">
-        <v>0.1534830042586304</v>
+        <v>0.1615011898950057</v>
       </c>
       <c r="M28" t="n">
-        <v>12.88741183508755</v>
+        <v>12.94150456211317</v>
       </c>
       <c r="N28" t="n">
-        <v>260.4406011339353</v>
+        <v>261.6339788724767</v>
       </c>
       <c r="O28" t="n">
-        <v>16.138172174504</v>
+        <v>16.17510367424199</v>
       </c>
       <c r="P28" t="n">
-        <v>278.0637249892663</v>
+        <v>277.7841018477191</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -35679,7 +35885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC321"/>
+  <dimension ref="A1:AC323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82431,17 +82637,17 @@
       </c>
       <c r="W321" t="inlineStr">
         <is>
-          <t>-43.217736018407194,170.16477693965265</t>
+          <t>-43.21792590664016,170.16496236191833</t>
         </is>
       </c>
       <c r="X321" t="inlineStr">
         <is>
-          <t>-43.217230245702076,170.16534172180454</t>
+          <t>-43.217411942742466,170.1655637583436</t>
         </is>
       </c>
       <c r="Y321" t="inlineStr">
         <is>
-          <t>-43.216812542619756,170.16595669248957</t>
+          <t>-43.216979933764925,170.16624425151727</t>
         </is>
       </c>
       <c r="Z321" t="inlineStr">
@@ -82462,6 +82668,300 @@
       <c r="AC321" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-12 22:19:57+00:00</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>-43.22606925083182,170.15016483735573</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>-43.225962916225825,170.1510645053035</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>-43.22569204190335,170.15188624867645</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>-43.22536662579669,170.15263147459987</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-43.22501744859033,170.15331996376858</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>-43.22458702149682,170.15399077810292</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>-43.22412500338569,170.15463573044872</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>-43.22363575141486,170.15525179387618</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>-43.22310194838216,170.1557672313138</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>-43.22271342344213,170.15641895040002</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>-43.22226510021104,170.1570540654145</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>-43.22176090851114,170.1576302229095</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>-43.22126742741216,170.1582216546335</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>-43.22066823368218,170.15866238918338</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>-43.220196859122886,170.15928534617095</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>-43.2197455415661,170.16000724277802</t>
+        </is>
+      </c>
+      <c r="R322" t="inlineStr">
+        <is>
+          <t>-43.21946336416071,170.16093150982172</t>
+        </is>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>-43.21905024968292,170.16165136991896</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>-43.21865891819625,170.16237146188112</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>-43.21861404366176,170.16342985839637</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>-43.21882759558993,170.1647406180675</t>
+        </is>
+      </c>
+      <c r="W322" t="inlineStr">
+        <is>
+          <t>-43.21882598631743,170.16584129179827</t>
+        </is>
+      </c>
+      <c r="X322" t="inlineStr">
+        <is>
+          <t>-43.21738403066769,170.1655296492477</t>
+        </is>
+      </c>
+      <c r="Y322" t="inlineStr">
+        <is>
+          <t>-43.216875979853334,170.16606567014634</t>
+        </is>
+      </c>
+      <c r="Z322" t="inlineStr">
+        <is>
+          <t>-43.21632378933475,170.16654092064036</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>-43.215829388137294,170.16713690349204</t>
+        </is>
+      </c>
+      <c r="AB322" t="inlineStr">
+        <is>
+          <t>-43.21540464620649,170.16786791003034</t>
+        </is>
+      </c>
+      <c r="AC322" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-28 22:20:04+00:00</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>-43.226041359973934,170.15015162858464</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>-43.22597941261139,170.1510723179732</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>-43.225719932646385,170.15189945793043</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>-43.225407736317436,170.1526604621889</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-43.2250486363462,170.15335169913084</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>-43.224606360945614,170.15401129452744</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>-43.224143418454354,170.15465526629902</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>-43.22364463896587,170.15526122236096</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>-43.223130747904925,170.15580126722347</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>-43.222752342434596,170.1564722329326</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>-43.22229064012485,170.15709047472114</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>-43.22177050150842,170.15764389855056</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>-43.221265060320164,170.15821828013554</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>-43.22065770638382,170.15864738164709</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>-43.220208881357266,170.15930248492194</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>-43.21975333456634,170.1600171052373</t>
+        </is>
+      </c>
+      <c r="R323" t="inlineStr">
+        <is>
+          <t>-43.21940392045581,170.16086926884788</t>
+        </is>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>-43.21898719654163,170.16158980219276</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>-43.21858839561861,170.16230260026276</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>-43.21867372745845,170.16348813783316</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>-43.21910294403432,170.16500949689487</t>
+        </is>
+      </c>
+      <c r="W323" t="inlineStr">
+        <is>
+          <t>-43.21910931498129,170.16611796942325</t>
+        </is>
+      </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>-43.217263055869275,170.1653818161931</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>-43.216820332179346,170.16597007400935</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>-43.216318498256825,170.1665306655393</t>
+        </is>
+      </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>-43.21583685783783,170.16715138122726</t>
+        </is>
+      </c>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>-43.2153914187338,170.16784227242562</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
